--- a/DataAnalysis/TryingToPackStuffBetter/MLT/LT/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/MLT/LT/0.05/Results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\MLT\CS\0.05\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\MLT\LT\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A67A13-6F9E-42CA-9A72-9DEA5AD64762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC20EFC8-F82C-4828-8518-ED25AF98C1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -511,31 +511,71 @@
       <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
+      <c r="E4" s="1">
+        <v>34.875</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3.9893323661074827</v>
+      </c>
+      <c r="G4" s="1">
+        <v>32.625</v>
+      </c>
+      <c r="H4" s="1">
+        <v>4.3123764804445024</v>
+      </c>
+      <c r="I4" s="1">
+        <v>10.041666666666666</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.8642367842843341</v>
+      </c>
+      <c r="K4" s="1">
+        <v>25.847222222222225</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2.4827265206685523</v>
+      </c>
+      <c r="M4" s="1">
+        <v>15.805555555555552</v>
+      </c>
+      <c r="N4" s="1">
+        <v>2.6919570941293043</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="E5" s="1">
+        <v>27.384615384615383</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3.1632910483245631</v>
+      </c>
+      <c r="G5" s="1">
+        <v>28.076923076923077</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2.8346527847791889</v>
+      </c>
+      <c r="I5" s="1">
+        <v>10.153846153846153</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2.8165035607455393</v>
+      </c>
+      <c r="K5" s="1">
+        <v>21.871794871794869</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1.5872084832279494</v>
+      </c>
+      <c r="M5" s="1">
+        <v>11.717948717948719</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1.9876757031403984</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
@@ -556,16 +596,36 @@
       <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
+      <c r="E7" s="1">
+        <v>27.888888888888889</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2.2607766610417559</v>
+      </c>
+      <c r="G7" s="1">
+        <v>27.166666666666668</v>
+      </c>
+      <c r="H7" s="1">
+        <v>4.1155194082885824</v>
+      </c>
+      <c r="I7" s="1">
+        <v>9.3888888888888893</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2.19057323801582</v>
+      </c>
+      <c r="K7" s="1">
+        <v>21.481481481481485</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1.0943175335329001</v>
+      </c>
+      <c r="M7" s="1">
+        <v>12.092592592592592</v>
+      </c>
+      <c r="N7" s="1">
+        <v>2.245537412648682</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
@@ -586,16 +646,36 @@
       <c r="D9" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
+      <c r="E9" s="1">
+        <v>27.944444444444443</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2.6509956200978113</v>
+      </c>
+      <c r="G9" s="1">
+        <v>27.722222222222221</v>
+      </c>
+      <c r="H9" s="1">
+        <v>3.2510682005218619</v>
+      </c>
+      <c r="I9" s="1">
+        <v>10.333333333333334</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2.5248762345905194</v>
+      </c>
+      <c r="K9" s="1">
+        <v>22.000000000000004</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1.8123802642442959</v>
+      </c>
+      <c r="M9" s="1">
+        <v>11.666666666666666</v>
+      </c>
+      <c r="N9" s="1">
+        <v>2.1098314835286929</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -616,31 +696,71 @@
       <c r="B11" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+      <c r="E11" s="1">
+        <v>23.166666666666668</v>
+      </c>
+      <c r="F11" s="1">
+        <v>4.0083246708153144</v>
+      </c>
+      <c r="G11" s="1">
+        <v>22.083333333333332</v>
+      </c>
+      <c r="H11" s="1">
+        <v>3.7870393009139338</v>
+      </c>
+      <c r="I11" s="1">
+        <v>10.833333333333334</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2.3593784492248533</v>
+      </c>
+      <c r="K11" s="1">
+        <v>18.694444444444446</v>
+      </c>
+      <c r="L11" s="1">
+        <v>2.3176057249446593</v>
+      </c>
+      <c r="M11" s="1">
+        <v>7.8611111111111116</v>
+      </c>
+      <c r="N11" s="1">
+        <v>2.4819720355364976</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="E12" s="1">
+        <v>18.818181818181817</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4.314352368969919</v>
+      </c>
+      <c r="G12" s="1">
+        <v>19.318181818181817</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3.7965295157072592</v>
+      </c>
+      <c r="I12" s="1">
+        <v>9.2727272727272734</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1.5060484116328443</v>
+      </c>
+      <c r="K12" s="1">
+        <v>15.803030303030305</v>
+      </c>
+      <c r="L12" s="1">
+        <v>2.7078262928635644</v>
+      </c>
+      <c r="M12" s="1">
+        <v>6.5303030303030312</v>
+      </c>
+      <c r="N12" s="1">
+        <v>2.3055707678699764</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
@@ -661,16 +781,36 @@
       <c r="C14" t="s">
         <v>1</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
+      <c r="E14" s="1">
+        <v>20.9375</v>
+      </c>
+      <c r="F14" s="1">
+        <v>4.9239756004965862</v>
+      </c>
+      <c r="G14" s="1">
+        <v>21.125</v>
+      </c>
+      <c r="H14" s="1">
+        <v>3.9888236719256325</v>
+      </c>
+      <c r="I14" s="1">
+        <v>9.125</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2.2951812875799469</v>
+      </c>
+      <c r="K14" s="1">
+        <v>17.0625</v>
+      </c>
+      <c r="L14" s="1">
+        <v>2.7035213662513864</v>
+      </c>
+      <c r="M14" s="1">
+        <v>7.9375</v>
+      </c>
+      <c r="N14" s="1">
+        <v>3.1319367454943587</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
@@ -691,16 +831,36 @@
       <c r="D16" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
+      <c r="E16" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="F16" s="1">
+        <v>4.2367440328629771</v>
+      </c>
+      <c r="G16" s="1">
+        <v>21.1</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3.0495901363953739</v>
+      </c>
+      <c r="I16" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1.2041594578792247</v>
+      </c>
+      <c r="K16" s="1">
+        <v>17.833333333333336</v>
+      </c>
+      <c r="L16" s="1">
+        <v>2.1698694277152386</v>
+      </c>
+      <c r="M16" s="1">
+        <v>7.1333333333333346</v>
+      </c>
+      <c r="N16" s="1">
+        <v>2.4307063445289541</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -710,7 +870,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
-  <dimension ref="A2:AF4"/>
+  <dimension ref="A2:AF8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -779,104 +939,352 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G4">
+        <v>93</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
+      </c>
+      <c r="I4">
+        <v>26</v>
+      </c>
+      <c r="J4">
+        <v>74</v>
+      </c>
+      <c r="L4">
+        <v>91</v>
+      </c>
+      <c r="M4">
+        <v>9</v>
+      </c>
+      <c r="N4">
+        <v>15</v>
+      </c>
+      <c r="O4">
         <v>85</v>
-      </c>
-      <c r="H4">
-        <v>15</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-      <c r="J4">
-        <v>88</v>
-      </c>
-      <c r="L4">
-        <v>59</v>
-      </c>
-      <c r="M4">
-        <v>41</v>
-      </c>
-      <c r="N4">
-        <v>28</v>
-      </c>
-      <c r="O4">
-        <v>72</v>
       </c>
       <c r="Q4">
         <f>AVERAGE(C4,D4)</f>
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="R4">
         <f>AVERAGE(H4,I4)</f>
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="S4">
         <f>AVERAGE(M4,N4)</f>
-        <v>34.5</v>
+        <v>12</v>
       </c>
       <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>24.5</v>
+        <v>16.166666666666668</v>
       </c>
       <c r="U4">
         <f>MIN(Q4:S4)</f>
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="V4">
         <f>T4-U4</f>
-        <v>11</v>
+        <v>4.1666666666666679</v>
       </c>
       <c r="W4">
         <f>AVERAGE(Q4:Q15)</f>
-        <v>25.5</v>
-      </c>
-      <c r="X4" t="e">
+        <v>21.7</v>
+      </c>
+      <c r="X4">
         <f>_xlfn.STDEV.S(Q4:Q15)</f>
-        <v>#DIV/0!</v>
+        <v>4.2367440328629771</v>
       </c>
       <c r="Y4">
         <f>AVERAGE(R4:R15)</f>
-        <v>13.5</v>
-      </c>
-      <c r="Z4" t="e">
+        <v>21.1</v>
+      </c>
+      <c r="Z4">
         <f>_xlfn.STDEV.S(R4:R15)</f>
-        <v>#DIV/0!</v>
+        <v>3.0495901363953739</v>
       </c>
       <c r="AA4">
         <f>AVERAGE(S4:S15)</f>
-        <v>34.5</v>
-      </c>
-      <c r="AB4" t="e">
+        <v>10.7</v>
+      </c>
+      <c r="AB4">
         <f>_xlfn.STDEV.S(S4:S15)</f>
-        <v>#DIV/0!</v>
+        <v>1.2041594578792247</v>
       </c>
       <c r="AC4">
         <f>AVERAGE(T4:T15)</f>
-        <v>24.5</v>
-      </c>
-      <c r="AD4" t="e">
+        <v>17.833333333333336</v>
+      </c>
+      <c r="AD4">
         <f>_xlfn.STDEV.S(T4:T15)</f>
-        <v>#DIV/0!</v>
+        <v>2.1698694277152386</v>
       </c>
       <c r="AE4">
         <f>AVERAGE(V4:V15)</f>
+        <v>7.1333333333333346</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(V4:V15)</f>
+        <v>2.4307063445289541</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>78</v>
+      </c>
+      <c r="C5">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>80</v>
+      </c>
+      <c r="G5">
+        <v>87</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>29</v>
+      </c>
+      <c r="J5">
+        <v>71</v>
+      </c>
+      <c r="L5">
+        <v>92</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
+      <c r="N5">
+        <v>15</v>
+      </c>
+      <c r="O5">
+        <v>85</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q8" si="0">AVERAGE(C5,D5)</f>
+        <v>21</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R8" si="1">AVERAGE(H5,I5)</f>
+        <v>21</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S8" si="2">AVERAGE(M5,N5)</f>
+        <v>11.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T8" si="3">AVERAGE(Q5:S5)</f>
+        <v>17.833333333333332</v>
+      </c>
+      <c r="U5">
+        <f t="shared" ref="U5:U8" si="4">MIN(Q5:S5)</f>
+        <v>11.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" ref="V5:V8" si="5">T5-U5</f>
+        <v>6.3333333333333321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>81</v>
+      </c>
+      <c r="C6">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>35</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+      <c r="G6">
+        <v>86</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>36</v>
+      </c>
+      <c r="J6">
+        <v>64</v>
+      </c>
+      <c r="L6">
+        <v>88</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+      <c r="N6">
+        <v>8</v>
+      </c>
+      <c r="O6">
+        <v>92</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>20.666666666666668</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>10.666666666666668</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>87</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>81</v>
+      </c>
+      <c r="G7">
+        <v>91</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>33</v>
+      </c>
+      <c r="J7">
+        <v>67</v>
+      </c>
+      <c r="L7">
+        <v>91</v>
+      </c>
+      <c r="M7">
+        <v>9</v>
+      </c>
+      <c r="N7">
+        <v>9</v>
+      </c>
+      <c r="O7">
+        <v>91</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>15.333333333333334</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>6.3333333333333339</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>72</v>
+      </c>
+      <c r="C8">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>79</v>
+      </c>
+      <c r="G8">
+        <v>79</v>
+      </c>
+      <c r="H8">
+        <v>21</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>77</v>
+      </c>
+      <c r="L8">
+        <v>89</v>
+      </c>
+      <c r="M8">
         <v>11</v>
       </c>
-      <c r="AF4" t="e">
-        <f>_xlfn.STDEV.S(V4:V15)</f>
-        <v>#DIV/0!</v>
+      <c r="N8">
+        <v>11</v>
+      </c>
+      <c r="O8">
+        <v>89</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>24.5</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>8.1666666666666679</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C55A84A-0B17-453A-AC24-3659BE690EA1}">
-  <dimension ref="B2:AF4"/>
+  <dimension ref="B2:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:32" x14ac:dyDescent="0.3">
@@ -941,104 +1349,538 @@
     </row>
     <row r="4" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G4">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I4">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="J4">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="L4">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="M4">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="O4">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="Q4">
         <f>AVERAGE(C4,D4)</f>
-        <v>21.5</v>
+        <v>30</v>
       </c>
       <c r="R4">
         <f>AVERAGE(H4,I4)</f>
-        <v>12.5</v>
+        <v>28.5</v>
       </c>
       <c r="S4">
         <f>AVERAGE(M4,N4)</f>
-        <v>30.5</v>
+        <v>9.5</v>
       </c>
       <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>21.5</v>
+        <v>22.666666666666668</v>
       </c>
       <c r="U4">
         <f>MIN(Q4:S4)</f>
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="V4">
         <f>T4-U4</f>
-        <v>9</v>
+        <v>13.166666666666668</v>
       </c>
       <c r="W4">
         <f>AVERAGE(Q4:Q15)</f>
-        <v>21.5</v>
-      </c>
-      <c r="X4" t="e">
+        <v>20.9375</v>
+      </c>
+      <c r="X4">
         <f>_xlfn.STDEV.S(Q4:Q15)</f>
-        <v>#DIV/0!</v>
+        <v>4.9239756004965862</v>
       </c>
       <c r="Y4">
         <f>AVERAGE(R4:R15)</f>
-        <v>12.5</v>
-      </c>
-      <c r="Z4" t="e">
+        <v>21.125</v>
+      </c>
+      <c r="Z4">
         <f>_xlfn.STDEV.S(R4:R15)</f>
-        <v>#DIV/0!</v>
+        <v>3.9888236719256325</v>
       </c>
       <c r="AA4">
         <f>AVERAGE(S4:S15)</f>
-        <v>30.5</v>
-      </c>
-      <c r="AB4" t="e">
+        <v>9.125</v>
+      </c>
+      <c r="AB4">
         <f>_xlfn.STDEV.S(S4:S15)</f>
-        <v>#DIV/0!</v>
+        <v>2.2951812875799469</v>
       </c>
       <c r="AC4">
         <f>AVERAGE(T4:T15)</f>
-        <v>21.5</v>
-      </c>
-      <c r="AD4" t="e">
+        <v>17.0625</v>
+      </c>
+      <c r="AD4">
         <f>_xlfn.STDEV.S(T4:T15)</f>
-        <v>#DIV/0!</v>
+        <v>2.7035213662513864</v>
       </c>
       <c r="AE4">
         <f>AVERAGE(V4:V15)</f>
+        <v>7.9375</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(V4:V15)</f>
+        <v>3.1319367454943587</v>
+      </c>
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>82</v>
+      </c>
+      <c r="C5">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>78</v>
+      </c>
+      <c r="G5">
+        <v>90</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <v>74</v>
+      </c>
+      <c r="L5">
+        <v>97</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5">
+        <v>90</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q11" si="0">AVERAGE(C5,D5)</f>
+        <v>20</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R11" si="1">AVERAGE(H5,I5)</f>
+        <v>18</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S11" si="2">AVERAGE(M5,N5)</f>
+        <v>6.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T11" si="3">AVERAGE(Q5:S5)</f>
+        <v>14.833333333333334</v>
+      </c>
+      <c r="U5">
+        <f t="shared" ref="U5:U11" si="4">MIN(Q5:S5)</f>
+        <v>6.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" ref="V5:V11" si="5">T5-U5</f>
+        <v>8.3333333333333339</v>
+      </c>
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>85</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>74</v>
+      </c>
+      <c r="G6">
+        <v>94</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>36</v>
+      </c>
+      <c r="J6">
+        <v>64</v>
+      </c>
+      <c r="L6">
+        <v>96</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+      <c r="N6">
+        <v>6</v>
+      </c>
+      <c r="O6">
+        <v>94</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>15.5</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>83</v>
+      </c>
+      <c r="C7">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>86</v>
+      </c>
+      <c r="G7">
+        <v>92</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>34</v>
+      </c>
+      <c r="J7">
+        <v>66</v>
+      </c>
+      <c r="L7">
+        <v>95</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>16</v>
+      </c>
+      <c r="O7">
+        <v>84</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>10.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>15.666666666666666</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>10.5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>5.1666666666666661</v>
+      </c>
+    </row>
+    <row r="8" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>81</v>
+      </c>
+      <c r="C8">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>71</v>
+      </c>
+      <c r="G8">
+        <v>79</v>
+      </c>
+      <c r="H8">
+        <v>21</v>
+      </c>
+      <c r="I8">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>82</v>
+      </c>
+      <c r="L8">
+        <v>90</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+      <c r="N8">
+        <v>11</v>
+      </c>
+      <c r="O8">
+        <v>89</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>10.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>10.5</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>84</v>
+      </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9">
+        <v>85</v>
+      </c>
+      <c r="G9">
+        <v>90</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>36</v>
+      </c>
+      <c r="J9">
+        <v>64</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9">
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <v>13</v>
+      </c>
+      <c r="O9">
+        <v>87</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="AF4" t="e">
-        <f>_xlfn.STDEV.S(V4:V15)</f>
-        <v>#DIV/0!</v>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>15.833333333333334</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>6.8333333333333339</v>
+      </c>
+    </row>
+    <row r="10" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>78</v>
+      </c>
+      <c r="C10">
+        <v>22</v>
+      </c>
+      <c r="D10">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>86</v>
+      </c>
+      <c r="G10">
+        <v>86</v>
+      </c>
+      <c r="H10">
+        <v>14</v>
+      </c>
+      <c r="I10">
+        <v>16</v>
+      </c>
+      <c r="J10">
+        <v>84</v>
+      </c>
+      <c r="L10">
+        <v>91</v>
+      </c>
+      <c r="M10">
+        <v>9</v>
+      </c>
+      <c r="N10">
+        <v>15</v>
+      </c>
+      <c r="O10">
+        <v>85</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>85</v>
+      </c>
+      <c r="C11">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>33</v>
+      </c>
+      <c r="E11">
+        <v>67</v>
+      </c>
+      <c r="G11">
+        <v>92</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>38</v>
+      </c>
+      <c r="J11">
+        <v>62</v>
+      </c>
+      <c r="L11">
+        <v>95</v>
+      </c>
+      <c r="M11">
+        <v>5</v>
+      </c>
+      <c r="N11">
+        <v>15</v>
+      </c>
+      <c r="O11">
+        <v>85</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1048,7 +1890,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
-  <dimension ref="A2:AF4"/>
+  <dimension ref="A2:AF14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -1117,104 +1959,724 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G4">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I4">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J4">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="L4">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="M4">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="N4">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="O4">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="Q4">
         <f>AVERAGE(C4,D4)</f>
-        <v>23.5</v>
+        <v>14</v>
       </c>
       <c r="R4">
         <f>AVERAGE(H4,I4)</f>
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="S4">
         <f>AVERAGE(M4,N4)</f>
-        <v>35.5</v>
+        <v>11</v>
       </c>
       <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>24.833333333333332</v>
+        <v>14.833333333333334</v>
       </c>
       <c r="U4">
         <f>MIN(Q4:S4)</f>
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="V4">
         <f>T4-U4</f>
-        <v>9.3333333333333321</v>
+        <v>3.8333333333333339</v>
       </c>
       <c r="W4">
-        <f>AVERAGE(Q4:Q12)</f>
-        <v>23.5</v>
-      </c>
-      <c r="X4" t="e">
-        <f>_xlfn.STDEV.S(Q4:Q12)</f>
-        <v>#DIV/0!</v>
+        <f>AVERAGE(Q4:Q19)</f>
+        <v>18.818181818181817</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(Q4:Q19)</f>
+        <v>4.314352368969919</v>
       </c>
       <c r="Y4">
-        <f>AVERAGE(R4:R12)</f>
+        <f>AVERAGE(R4:R19)</f>
+        <v>19.318181818181817</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(R4:R19)</f>
+        <v>3.7965295157072592</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(S4:S19)</f>
+        <v>9.2727272727272734</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(S4:S19)</f>
+        <v>1.5060484116328443</v>
+      </c>
+      <c r="AC4">
+        <f>AVERAGE(T4:T19)</f>
+        <v>15.803030303030305</v>
+      </c>
+      <c r="AD4">
+        <f>_xlfn.STDEV.S(T4:T19)</f>
+        <v>2.7078262928635644</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(V4:V19)</f>
+        <v>6.5303030303030312</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(V4:V19)</f>
+        <v>2.3055707678699764</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>84</v>
+      </c>
+      <c r="G5">
+        <v>93</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <v>74</v>
+      </c>
+      <c r="L5">
+        <v>94</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+      <c r="N5">
+        <v>12</v>
+      </c>
+      <c r="O5">
+        <v>88</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q14" si="0">AVERAGE(C5,D5)</f>
+        <v>18</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R14" si="1">AVERAGE(H5,I5)</f>
+        <v>16.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S14" si="2">AVERAGE(M5,N5)</f>
+        <v>9</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T14" si="3">AVERAGE(Q5:S5)</f>
+        <v>14.5</v>
+      </c>
+      <c r="U5">
+        <f t="shared" ref="U5:U14" si="4">MIN(Q5:S5)</f>
+        <v>9</v>
+      </c>
+      <c r="V5">
+        <f t="shared" ref="V5:V14" si="5">T5-U5</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>84</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>74</v>
+      </c>
+      <c r="G6">
+        <v>94</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>29</v>
+      </c>
+      <c r="J6">
+        <v>71</v>
+      </c>
+      <c r="L6">
+        <v>96</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+      <c r="N6">
+        <v>12</v>
+      </c>
+      <c r="O6">
+        <v>88</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
-      <c r="Z4" t="e">
-        <f>_xlfn.STDEV.S(R4:R12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(S4:S12)</f>
-        <v>35.5</v>
-      </c>
-      <c r="AB4" t="e">
-        <f>_xlfn.STDEV.S(S4:S12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC4">
-        <f>AVERAGE(T4:T12)</f>
-        <v>24.833333333333332</v>
-      </c>
-      <c r="AD4" t="e">
-        <f>_xlfn.STDEV.S(T4:T12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(V4:V12)</f>
-        <v>9.3333333333333321</v>
-      </c>
-      <c r="AF4" t="e">
-        <f>_xlfn.STDEV.S(V4:V12)</f>
-        <v>#DIV/0!</v>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>86</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>80</v>
+      </c>
+      <c r="G7">
+        <v>95</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>31</v>
+      </c>
+      <c r="J7">
+        <v>69</v>
+      </c>
+      <c r="L7">
+        <v>95</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>8</v>
+      </c>
+      <c r="O7">
+        <v>92</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>6.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>13.833333333333334</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>6.5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>7.3333333333333339</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>70</v>
+      </c>
+      <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>73</v>
+      </c>
+      <c r="G8">
+        <v>87</v>
+      </c>
+      <c r="H8">
+        <v>13</v>
+      </c>
+      <c r="I8">
+        <v>39</v>
+      </c>
+      <c r="J8">
+        <v>61</v>
+      </c>
+      <c r="L8">
+        <v>94</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+      <c r="N8">
+        <v>13</v>
+      </c>
+      <c r="O8">
+        <v>87</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>28.5</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>9.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>11.833333333333332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>85</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>22</v>
+      </c>
+      <c r="E9">
+        <v>78</v>
+      </c>
+      <c r="G9">
+        <v>89</v>
+      </c>
+      <c r="H9">
+        <v>11</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>77</v>
+      </c>
+      <c r="L9">
+        <v>93</v>
+      </c>
+      <c r="M9">
+        <v>7</v>
+      </c>
+      <c r="N9">
+        <v>11</v>
+      </c>
+      <c r="O9">
+        <v>89</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>18.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>14.833333333333334</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>5.8333333333333339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>82</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>26</v>
+      </c>
+      <c r="E10">
+        <v>74</v>
+      </c>
+      <c r="G10">
+        <v>81</v>
+      </c>
+      <c r="H10">
+        <v>19</v>
+      </c>
+      <c r="I10">
+        <v>32</v>
+      </c>
+      <c r="J10">
+        <v>68</v>
+      </c>
+      <c r="L10">
+        <v>93</v>
+      </c>
+      <c r="M10">
+        <v>7</v>
+      </c>
+      <c r="N10">
+        <v>14</v>
+      </c>
+      <c r="O10">
+        <v>86</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>25.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>10.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>10.5</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>8.8333333333333321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>79</v>
+      </c>
+      <c r="C11">
+        <v>21</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>80</v>
+      </c>
+      <c r="G11">
+        <v>85</v>
+      </c>
+      <c r="H11">
+        <v>15</v>
+      </c>
+      <c r="I11">
+        <v>23</v>
+      </c>
+      <c r="J11">
+        <v>77</v>
+      </c>
+      <c r="L11">
+        <v>94</v>
+      </c>
+      <c r="M11">
+        <v>6</v>
+      </c>
+      <c r="N11">
+        <v>15</v>
+      </c>
+      <c r="O11">
+        <v>85</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>10.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>10.5</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="5"/>
+        <v>6.1666666666666679</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>88</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+      <c r="D12">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>85</v>
+      </c>
+      <c r="G12">
+        <v>93</v>
+      </c>
+      <c r="H12">
+        <v>7</v>
+      </c>
+      <c r="I12">
+        <v>32</v>
+      </c>
+      <c r="J12">
+        <v>68</v>
+      </c>
+      <c r="L12">
+        <v>93</v>
+      </c>
+      <c r="M12">
+        <v>7</v>
+      </c>
+      <c r="N12">
+        <v>10</v>
+      </c>
+      <c r="O12">
+        <v>90</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="2"/>
+        <v>8.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="3"/>
+        <v>13.833333333333334</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="4"/>
+        <v>8.5</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="5"/>
+        <v>5.3333333333333339</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>82</v>
+      </c>
+      <c r="C13">
+        <v>18</v>
+      </c>
+      <c r="D13">
+        <v>11</v>
+      </c>
+      <c r="E13">
+        <v>89</v>
+      </c>
+      <c r="G13">
+        <v>92</v>
+      </c>
+      <c r="H13">
+        <v>8</v>
+      </c>
+      <c r="I13">
+        <v>18</v>
+      </c>
+      <c r="J13">
+        <v>82</v>
+      </c>
+      <c r="L13">
+        <v>93</v>
+      </c>
+      <c r="M13">
+        <v>7</v>
+      </c>
+      <c r="N13">
+        <v>9</v>
+      </c>
+      <c r="O13">
+        <v>91</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="3"/>
+        <v>11.833333333333334</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333339</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>78</v>
+      </c>
+      <c r="C14">
+        <v>22</v>
+      </c>
+      <c r="D14">
+        <v>17</v>
+      </c>
+      <c r="E14">
+        <v>83</v>
+      </c>
+      <c r="G14">
+        <v>77</v>
+      </c>
+      <c r="H14">
+        <v>23</v>
+      </c>
+      <c r="I14">
+        <v>19</v>
+      </c>
+      <c r="J14">
+        <v>81</v>
+      </c>
+      <c r="L14">
+        <v>98</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>21</v>
+      </c>
+      <c r="O14">
+        <v>79</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="2"/>
+        <v>11.5</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="3"/>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="4"/>
+        <v>11.5</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="5"/>
+        <v>5.8333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -1224,7 +2686,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
-  <dimension ref="A2:AF4"/>
+  <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -1293,104 +2755,414 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="G4">
+        <v>80</v>
+      </c>
+      <c r="H4">
+        <v>20</v>
+      </c>
+      <c r="I4">
+        <v>22</v>
+      </c>
+      <c r="J4">
+        <v>78</v>
+      </c>
+      <c r="L4">
+        <v>89</v>
+      </c>
+      <c r="M4">
+        <v>11</v>
+      </c>
+      <c r="N4">
+        <v>16</v>
+      </c>
+      <c r="O4">
         <v>84</v>
-      </c>
-      <c r="H4">
-        <v>16</v>
-      </c>
-      <c r="I4">
-        <v>16</v>
-      </c>
-      <c r="J4">
-        <v>84</v>
-      </c>
-      <c r="L4">
-        <v>65</v>
-      </c>
-      <c r="M4">
-        <v>35</v>
-      </c>
-      <c r="N4">
-        <v>41</v>
-      </c>
-      <c r="O4">
-        <v>59</v>
       </c>
       <c r="Q4">
         <f>AVERAGE(C4,D4)</f>
-        <v>22.5</v>
+        <v>21</v>
       </c>
       <c r="R4">
         <f>AVERAGE(H4,I4)</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="S4">
         <f>AVERAGE(M4,N4)</f>
-        <v>38</v>
+        <v>13.5</v>
       </c>
       <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
       <c r="U4">
         <f>MIN(Q4:S4)</f>
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="V4">
         <f>T4-U4</f>
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <f>AVERAGE(Q4:Q12)</f>
-        <v>22.5</v>
-      </c>
-      <c r="X4" t="e">
+        <v>23.166666666666668</v>
+      </c>
+      <c r="X4">
         <f>_xlfn.STDEV.S(Q4:Q12)</f>
-        <v>#DIV/0!</v>
+        <v>4.0083246708153144</v>
       </c>
       <c r="Y4">
         <f>AVERAGE(R4:R12)</f>
-        <v>16</v>
-      </c>
-      <c r="Z4" t="e">
+        <v>22.083333333333332</v>
+      </c>
+      <c r="Z4">
         <f>_xlfn.STDEV.S(R4:R12)</f>
-        <v>#DIV/0!</v>
+        <v>3.7870393009139338</v>
       </c>
       <c r="AA4">
         <f>AVERAGE(S4:S12)</f>
-        <v>38</v>
-      </c>
-      <c r="AB4" t="e">
+        <v>10.833333333333334</v>
+      </c>
+      <c r="AB4">
         <f>_xlfn.STDEV.S(S4:S12)</f>
-        <v>#DIV/0!</v>
+        <v>2.3593784492248533</v>
       </c>
       <c r="AC4">
         <f>AVERAGE(T4:T12)</f>
-        <v>25.5</v>
-      </c>
-      <c r="AD4" t="e">
+        <v>18.694444444444446</v>
+      </c>
+      <c r="AD4">
         <f>_xlfn.STDEV.S(T4:T12)</f>
-        <v>#DIV/0!</v>
+        <v>2.3176057249446593</v>
       </c>
       <c r="AE4">
         <f>AVERAGE(V4:V12)</f>
+        <v>7.8611111111111116</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(V4:V12)</f>
+        <v>2.4819720355364976</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>75</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
+      </c>
+      <c r="E5">
+        <v>85</v>
+      </c>
+      <c r="G5">
+        <v>86</v>
+      </c>
+      <c r="H5">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>36</v>
+      </c>
+      <c r="J5">
+        <v>64</v>
+      </c>
+      <c r="L5">
+        <v>92</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
+      <c r="N5">
+        <v>13</v>
+      </c>
+      <c r="O5">
+        <v>87</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
+        <v>20</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
+        <v>25</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
+        <v>10.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
+        <v>18.5</v>
+      </c>
+      <c r="U5">
+        <f t="shared" ref="U5:U9" si="4">MIN(Q5:S5)</f>
+        <v>10.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" ref="V5:V9" si="5">T5-U5</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>62</v>
+      </c>
+      <c r="C6">
+        <v>38</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>86</v>
+      </c>
+      <c r="G6">
+        <v>84</v>
+      </c>
+      <c r="H6">
+        <v>16</v>
+      </c>
+      <c r="I6">
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <v>82</v>
+      </c>
+      <c r="L6">
+        <v>94</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <v>8</v>
+      </c>
+      <c r="O6">
+        <v>92</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>9.6666666666666679</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>91</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>72</v>
+      </c>
+      <c r="G7">
+        <v>91</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>70</v>
+      </c>
+      <c r="L7">
+        <v>87</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+      <c r="N7">
+        <v>11</v>
+      </c>
+      <c r="O7">
+        <v>89</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>18.5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>4.6666666666666679</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>67</v>
+      </c>
+      <c r="C8">
+        <v>33</v>
+      </c>
+      <c r="D8">
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>75</v>
+      </c>
+      <c r="G8">
+        <v>76</v>
+      </c>
+      <c r="H8">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <v>31</v>
+      </c>
+      <c r="J8">
+        <v>69</v>
+      </c>
+      <c r="L8">
+        <v>88</v>
+      </c>
+      <c r="M8">
+        <v>12</v>
+      </c>
+      <c r="N8">
+        <v>13</v>
+      </c>
+      <c r="O8">
+        <v>87</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>12.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>12.5</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>68</v>
+      </c>
+      <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="D9">
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>83</v>
+      </c>
+      <c r="G9">
+        <v>75</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>20</v>
+      </c>
+      <c r="J9">
+        <v>80</v>
+      </c>
+      <c r="L9">
+        <v>89</v>
+      </c>
+      <c r="M9">
+        <v>11</v>
+      </c>
+      <c r="N9">
+        <v>8</v>
+      </c>
+      <c r="O9">
+        <v>92</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>24.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>22.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
         <v>9.5</v>
       </c>
-      <c r="AF4" t="e">
-        <f>_xlfn.STDEV.S(V4:V12)</f>
-        <v>#DIV/0!</v>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>18.833333333333332</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>9.3333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -1400,7 +3172,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
-  <dimension ref="A2:AF4"/>
+  <dimension ref="A2:AF12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -1469,104 +3241,600 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H4">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="J4">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="L4">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="M4">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="O4">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="Q4">
         <f>AVERAGE(C4,D4)</f>
-        <v>25</v>
+        <v>33.5</v>
       </c>
       <c r="R4">
         <f>AVERAGE(H4,I4)</f>
-        <v>12</v>
+        <v>31.5</v>
       </c>
       <c r="S4">
         <f>AVERAGE(M4,N4)</f>
-        <v>30.5</v>
+        <v>10.5</v>
       </c>
       <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>22.5</v>
+        <v>25.166666666666668</v>
       </c>
       <c r="U4">
         <f>MIN(Q4:S4)</f>
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="V4">
         <f>T4-U4</f>
-        <v>10.5</v>
+        <v>14.666666666666668</v>
       </c>
       <c r="W4">
         <f>AVERAGE(Q4:Q12)</f>
-        <v>25</v>
-      </c>
-      <c r="X4" t="e">
+        <v>27.944444444444443</v>
+      </c>
+      <c r="X4">
         <f>_xlfn.STDEV.S(Q4:Q12)</f>
-        <v>#DIV/0!</v>
+        <v>2.6509956200978113</v>
       </c>
       <c r="Y4">
         <f>AVERAGE(R4:R12)</f>
-        <v>12</v>
-      </c>
-      <c r="Z4" t="e">
+        <v>27.722222222222221</v>
+      </c>
+      <c r="Z4">
         <f>_xlfn.STDEV.S(R4:R12)</f>
-        <v>#DIV/0!</v>
+        <v>3.2510682005218619</v>
       </c>
       <c r="AA4">
         <f>AVERAGE(S4:S12)</f>
-        <v>30.5</v>
-      </c>
-      <c r="AB4" t="e">
+        <v>10.333333333333334</v>
+      </c>
+      <c r="AB4">
         <f>_xlfn.STDEV.S(S4:S12)</f>
-        <v>#DIV/0!</v>
+        <v>2.5248762345905194</v>
       </c>
       <c r="AC4">
         <f>AVERAGE(T4:T12)</f>
-        <v>22.5</v>
-      </c>
-      <c r="AD4" t="e">
+        <v>22.000000000000004</v>
+      </c>
+      <c r="AD4">
         <f>_xlfn.STDEV.S(T4:T12)</f>
-        <v>#DIV/0!</v>
+        <v>1.8123802642442959</v>
       </c>
       <c r="AE4">
         <f>AVERAGE(V4:V12)</f>
-        <v>10.5</v>
-      </c>
-      <c r="AF4" t="e">
+        <v>11.666666666666666</v>
+      </c>
+      <c r="AF4">
         <f>_xlfn.STDEV.S(V4:V12)</f>
-        <v>#DIV/0!</v>
+        <v>2.1098314835286929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>71</v>
+      </c>
+      <c r="C5">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>27</v>
+      </c>
+      <c r="E5">
+        <v>73</v>
+      </c>
+      <c r="G5">
+        <v>89</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>35</v>
+      </c>
+      <c r="J5">
+        <v>65</v>
+      </c>
+      <c r="L5">
+        <v>87</v>
+      </c>
+      <c r="M5">
+        <v>13</v>
+      </c>
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5">
+        <v>90</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q12" si="0">AVERAGE(C5,D5)</f>
+        <v>28</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R12" si="1">AVERAGE(H5,I5)</f>
+        <v>23</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S12" si="2">AVERAGE(M5,N5)</f>
+        <v>11.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T12" si="3">AVERAGE(Q5:S5)</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="U5">
+        <f t="shared" ref="U5:U12" si="4">MIN(Q5:S5)</f>
+        <v>11.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" ref="V5:V12" si="5">T5-U5</f>
+        <v>9.3333333333333321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>65</v>
+      </c>
+      <c r="C6">
+        <v>35</v>
+      </c>
+      <c r="D6">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>77</v>
+      </c>
+      <c r="G6">
+        <v>85</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>31</v>
+      </c>
+      <c r="J6">
+        <v>69</v>
+      </c>
+      <c r="L6">
+        <v>87</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+      <c r="N6">
+        <v>9</v>
+      </c>
+      <c r="O6">
+        <v>91</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>68</v>
+      </c>
+      <c r="C7">
+        <v>32</v>
+      </c>
+      <c r="D7">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>76</v>
+      </c>
+      <c r="G7">
+        <v>76</v>
+      </c>
+      <c r="H7">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>40</v>
+      </c>
+      <c r="J7">
+        <v>60</v>
+      </c>
+      <c r="L7">
+        <v>93</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+      <c r="N7">
+        <v>15</v>
+      </c>
+      <c r="O7">
+        <v>85</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>12.666666666666668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>74</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>75</v>
+      </c>
+      <c r="G8">
+        <v>85</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>40</v>
+      </c>
+      <c r="J8">
+        <v>60</v>
+      </c>
+      <c r="L8">
+        <v>96</v>
+      </c>
+      <c r="M8">
+        <v>4</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8">
+        <v>96</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>25.5</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+      <c r="G9">
+        <v>82</v>
+      </c>
+      <c r="H9">
+        <v>18</v>
+      </c>
+      <c r="I9">
+        <v>39</v>
+      </c>
+      <c r="J9">
+        <v>61</v>
+      </c>
+      <c r="L9">
+        <v>92</v>
+      </c>
+      <c r="M9">
+        <v>8</v>
+      </c>
+      <c r="N9">
+        <v>14</v>
+      </c>
+      <c r="O9">
+        <v>86</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>29.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>28.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>72</v>
+      </c>
+      <c r="C10">
+        <v>28</v>
+      </c>
+      <c r="D10">
+        <v>27</v>
+      </c>
+      <c r="E10">
+        <v>73</v>
+      </c>
+      <c r="G10">
+        <v>86</v>
+      </c>
+      <c r="H10">
+        <v>14</v>
+      </c>
+      <c r="I10">
+        <v>39</v>
+      </c>
+      <c r="J10">
+        <v>61</v>
+      </c>
+      <c r="L10">
+        <v>92</v>
+      </c>
+      <c r="M10">
+        <v>8</v>
+      </c>
+      <c r="N10">
+        <v>16</v>
+      </c>
+      <c r="O10">
+        <v>84</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>27.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>26.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>80</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>29</v>
+      </c>
+      <c r="E11">
+        <v>71</v>
+      </c>
+      <c r="G11">
+        <v>82</v>
+      </c>
+      <c r="H11">
+        <v>18</v>
+      </c>
+      <c r="I11">
+        <v>42</v>
+      </c>
+      <c r="J11">
+        <v>58</v>
+      </c>
+      <c r="L11">
+        <v>90</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>15</v>
+      </c>
+      <c r="O11">
+        <v>85</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>24.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>12.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>12.5</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="5"/>
+        <v>9.8333333333333321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>76</v>
+      </c>
+      <c r="C12">
+        <v>24</v>
+      </c>
+      <c r="D12">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>72</v>
+      </c>
+      <c r="G12">
+        <v>84</v>
+      </c>
+      <c r="H12">
+        <v>16</v>
+      </c>
+      <c r="I12">
+        <v>39</v>
+      </c>
+      <c r="J12">
+        <v>61</v>
+      </c>
+      <c r="L12">
+        <v>90</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <v>9</v>
+      </c>
+      <c r="O12">
+        <v>91</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="2"/>
+        <v>9.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="5"/>
+        <v>11.5</v>
       </c>
     </row>
   </sheetData>
@@ -1576,7 +3844,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
-  <dimension ref="A2:AF35"/>
+  <dimension ref="A2:AF45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -2363,35 +4631,35 @@
       </c>
       <c r="U16">
         <f>AVERAGE(Q16:Q38)</f>
-        <v>25.9</v>
+        <v>26.6875</v>
       </c>
       <c r="V16">
         <f>_xlfn.STDEV.S(Q16:Q38)</f>
-        <v>4.6287147244132418</v>
+        <v>3.8999771061599104</v>
       </c>
       <c r="W16">
         <f>AVERAGE(R16:R38)</f>
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="X16">
         <f>_xlfn.STDEV.S(R16:R38)</f>
-        <v>1.8841443681416803</v>
+        <v>9.9857040670293102</v>
       </c>
       <c r="Y16">
         <f>AVERAGE(S16:S38)</f>
-        <v>36.200000000000003</v>
+        <v>22</v>
       </c>
       <c r="Z16">
         <f>_xlfn.STDEV.S(S16:S38)</f>
-        <v>2.7064737205448717</v>
+        <v>14.894869682449151</v>
       </c>
       <c r="AA16">
         <f>AVERAGE(T16:T38)</f>
-        <v>24.4</v>
+        <v>22.895833333333332</v>
       </c>
       <c r="AB16">
         <f>_xlfn.STDEV.S(T16:T38)</f>
-        <v>2.2441281405283231</v>
+        <v>1.8896911228247171</v>
       </c>
       <c r="AC16">
         <f t="shared" ref="AC16:AC19" si="10">MIN(Q16:S16)</f>
@@ -2401,13 +4669,13 @@
         <f t="shared" ref="AD16:AD19" si="11">T16-AC16</f>
         <v>12.833333333333332</v>
       </c>
-      <c r="AE16" t="e">
+      <c r="AE16">
         <f>AVERAGE(AD16:AD38)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF16" t="e">
+        <v>10.652196840039915</v>
+      </c>
+      <c r="AF16">
         <f>_xlfn.STDEV.S(AD16:AD38)</f>
-        <v>#DIV/0!</v>
+        <v>5.6480315878502276</v>
       </c>
     </row>
     <row r="17" spans="2:30" x14ac:dyDescent="0.3">
@@ -2653,104 +4921,724 @@
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C35">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D35">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E35">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G35">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H35">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I35">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="J35">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="L35">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="M35">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N35">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="O35">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="Q35">
         <f>AVERAGE(C35,D35)</f>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R35">
         <f>AVERAGE(H35,I35)</f>
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="S35">
         <f>AVERAGE(M35,N35)</f>
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <f>AVERAGE(Q35:S35)</f>
-        <v>26.333333333333332</v>
+        <v>22.666666666666668</v>
       </c>
       <c r="U35">
         <f>MIN(Q35:S35)</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <f>T35-U35</f>
-        <v>14.333333333333332</v>
+        <v>12.666666666666668</v>
       </c>
       <c r="W35">
         <f>AVERAGE(Q35:Q43)</f>
-        <v>29</v>
-      </c>
-      <c r="X35" t="e">
+        <v>27.888888888888889</v>
+      </c>
+      <c r="X35">
         <f>_xlfn.STDEV.S(Q35:Q43)</f>
-        <v>#DIV/0!</v>
+        <v>2.2607766610417559</v>
       </c>
       <c r="Y35">
         <f>AVERAGE(R35:R43)</f>
-        <v>12</v>
-      </c>
-      <c r="Z35" t="e">
+        <v>27.166666666666668</v>
+      </c>
+      <c r="Z35">
         <f>_xlfn.STDEV.S(R35:R43)</f>
-        <v>#DIV/0!</v>
+        <v>4.1155194082885824</v>
       </c>
       <c r="AA35">
         <f>AVERAGE(S35:S43)</f>
-        <v>38</v>
-      </c>
-      <c r="AB35" t="e">
+        <v>9.3888888888888893</v>
+      </c>
+      <c r="AB35">
         <f>_xlfn.STDEV.S(S35:S43)</f>
-        <v>#DIV/0!</v>
+        <v>2.19057323801582</v>
       </c>
       <c r="AC35">
         <f>AVERAGE(T35:T43)</f>
-        <v>26.333333333333332</v>
-      </c>
-      <c r="AD35" t="e">
+        <v>21.481481481481485</v>
+      </c>
+      <c r="AD35">
         <f>_xlfn.STDEV.S(T35:T43)</f>
-        <v>#DIV/0!</v>
+        <v>1.0943175335329001</v>
       </c>
       <c r="AE35">
         <f>AVERAGE(V35:V43)</f>
-        <v>14.333333333333332</v>
-      </c>
-      <c r="AF35" t="e">
+        <v>12.092592592592592</v>
+      </c>
+      <c r="AF35">
         <f>_xlfn.STDEV.S(V35:V43)</f>
-        <v>#DIV/0!</v>
+        <v>2.245537412648682</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>67</v>
+      </c>
+      <c r="C36">
+        <v>33</v>
+      </c>
+      <c r="D36">
+        <v>28</v>
+      </c>
+      <c r="E36">
+        <v>72</v>
+      </c>
+      <c r="G36">
+        <v>82</v>
+      </c>
+      <c r="H36">
+        <v>18</v>
+      </c>
+      <c r="I36">
+        <v>43</v>
+      </c>
+      <c r="J36">
+        <v>57</v>
+      </c>
+      <c r="L36">
+        <v>93</v>
+      </c>
+      <c r="M36">
+        <v>7</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36">
+        <v>97</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" ref="Q36:Q45" si="12">AVERAGE(C36,D36)</f>
+        <v>30.5</v>
+      </c>
+      <c r="R36">
+        <f t="shared" ref="R36:R45" si="13">AVERAGE(H36,I36)</f>
+        <v>30.5</v>
+      </c>
+      <c r="S36">
+        <f t="shared" ref="S36:S45" si="14">AVERAGE(M36,N36)</f>
+        <v>5</v>
+      </c>
+      <c r="T36">
+        <f t="shared" ref="T36:T45" si="15">AVERAGE(Q36:S36)</f>
+        <v>22</v>
+      </c>
+      <c r="U36">
+        <f t="shared" ref="U36:U45" si="16">MIN(Q36:S36)</f>
+        <v>5</v>
+      </c>
+      <c r="V36">
+        <f t="shared" ref="V36:V45" si="17">T36-U36</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>84</v>
+      </c>
+      <c r="C37">
+        <v>16</v>
+      </c>
+      <c r="D37">
+        <v>36</v>
+      </c>
+      <c r="E37">
+        <v>64</v>
+      </c>
+      <c r="G37">
+        <v>88</v>
+      </c>
+      <c r="H37">
+        <v>12</v>
+      </c>
+      <c r="I37">
+        <v>47</v>
+      </c>
+      <c r="J37">
+        <v>53</v>
+      </c>
+      <c r="L37">
+        <v>96</v>
+      </c>
+      <c r="M37">
+        <v>4</v>
+      </c>
+      <c r="N37">
+        <v>15</v>
+      </c>
+      <c r="O37">
+        <v>85</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="R37">
+        <f t="shared" si="13"/>
+        <v>29.5</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="14"/>
+        <v>9.5</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="15"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="16"/>
+        <v>9.5</v>
+      </c>
+      <c r="V37">
+        <f t="shared" si="17"/>
+        <v>12.166666666666668</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>71</v>
+      </c>
+      <c r="C38">
+        <v>29</v>
+      </c>
+      <c r="D38">
+        <v>30</v>
+      </c>
+      <c r="E38">
+        <v>70</v>
+      </c>
+      <c r="G38">
+        <v>86</v>
+      </c>
+      <c r="H38">
+        <v>14</v>
+      </c>
+      <c r="I38">
+        <v>37</v>
+      </c>
+      <c r="J38">
+        <v>63</v>
+      </c>
+      <c r="L38">
+        <v>95</v>
+      </c>
+      <c r="M38">
+        <v>5</v>
+      </c>
+      <c r="N38">
+        <v>12</v>
+      </c>
+      <c r="O38">
+        <v>88</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="12"/>
+        <v>29.5</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="13"/>
+        <v>25.5</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="14"/>
+        <v>8.5</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="15"/>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="16"/>
+        <v>8.5</v>
+      </c>
+      <c r="V38">
+        <f t="shared" si="17"/>
+        <v>12.666666666666668</v>
+      </c>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>75</v>
+      </c>
+      <c r="C39">
+        <v>25</v>
+      </c>
+      <c r="D39">
+        <v>27</v>
+      </c>
+      <c r="E39">
+        <v>73</v>
+      </c>
+      <c r="G39">
+        <v>85</v>
+      </c>
+      <c r="H39">
+        <v>15</v>
+      </c>
+      <c r="I39">
+        <v>32</v>
+      </c>
+      <c r="J39">
+        <v>68</v>
+      </c>
+      <c r="L39">
+        <v>92</v>
+      </c>
+      <c r="M39">
+        <v>8</v>
+      </c>
+      <c r="N39">
+        <v>8</v>
+      </c>
+      <c r="O39">
+        <v>92</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="R39">
+        <f t="shared" si="13"/>
+        <v>23.5</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="14"/>
+        <v>8</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="15"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="16"/>
+        <v>8</v>
+      </c>
+      <c r="V39">
+        <f t="shared" si="17"/>
+        <v>11.166666666666668</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>72</v>
+      </c>
+      <c r="C40">
+        <v>28</v>
+      </c>
+      <c r="D40">
+        <v>23</v>
+      </c>
+      <c r="E40">
+        <v>77</v>
+      </c>
+      <c r="G40">
+        <v>80</v>
+      </c>
+      <c r="H40">
+        <v>20</v>
+      </c>
+      <c r="I40">
+        <v>43</v>
+      </c>
+      <c r="J40">
+        <v>57</v>
+      </c>
+      <c r="L40">
+        <v>92</v>
+      </c>
+      <c r="M40">
+        <v>8</v>
+      </c>
+      <c r="N40">
+        <v>12</v>
+      </c>
+      <c r="O40">
+        <v>88</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="12"/>
+        <v>25.5</v>
+      </c>
+      <c r="R40">
+        <f t="shared" si="13"/>
+        <v>31.5</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="15"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="V40">
+        <f t="shared" si="17"/>
+        <v>12.333333333333332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>69</v>
+      </c>
+      <c r="C41">
+        <v>31</v>
+      </c>
+      <c r="D41">
+        <v>23</v>
+      </c>
+      <c r="E41">
+        <v>77</v>
+      </c>
+      <c r="G41">
+        <v>83</v>
+      </c>
+      <c r="H41">
+        <v>17</v>
+      </c>
+      <c r="I41">
+        <v>41</v>
+      </c>
+      <c r="J41">
+        <v>59</v>
+      </c>
+      <c r="L41">
+        <v>92</v>
+      </c>
+      <c r="M41">
+        <v>8</v>
+      </c>
+      <c r="N41">
+        <v>14</v>
+      </c>
+      <c r="O41">
+        <v>86</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="13"/>
+        <v>29</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="15"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="U41">
+        <f t="shared" si="16"/>
+        <v>11</v>
+      </c>
+      <c r="V41">
+        <f t="shared" si="17"/>
+        <v>11.333333333333332</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <v>63</v>
+      </c>
+      <c r="C42">
+        <v>37</v>
+      </c>
+      <c r="D42">
+        <v>18</v>
+      </c>
+      <c r="E42">
+        <v>82</v>
+      </c>
+      <c r="G42">
+        <v>79</v>
+      </c>
+      <c r="H42">
+        <v>21</v>
+      </c>
+      <c r="I42">
+        <v>28</v>
+      </c>
+      <c r="J42">
+        <v>72</v>
+      </c>
+      <c r="L42">
+        <v>95</v>
+      </c>
+      <c r="M42">
+        <v>5</v>
+      </c>
+      <c r="N42">
+        <v>14</v>
+      </c>
+      <c r="O42">
+        <v>86</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="12"/>
+        <v>27.5</v>
+      </c>
+      <c r="R42">
+        <f t="shared" si="13"/>
+        <v>24.5</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="14"/>
+        <v>9.5</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="15"/>
+        <v>20.5</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="16"/>
+        <v>9.5</v>
+      </c>
+      <c r="V42">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B43">
+        <v>69</v>
+      </c>
+      <c r="C43">
+        <v>31</v>
+      </c>
+      <c r="D43">
+        <v>33</v>
+      </c>
+      <c r="E43">
+        <v>67</v>
+      </c>
+      <c r="G43">
+        <v>90</v>
+      </c>
+      <c r="H43">
+        <v>10</v>
+      </c>
+      <c r="I43">
+        <v>29</v>
+      </c>
+      <c r="J43">
+        <v>71</v>
+      </c>
+      <c r="L43">
+        <v>89</v>
+      </c>
+      <c r="M43">
+        <v>11</v>
+      </c>
+      <c r="N43">
+        <v>15</v>
+      </c>
+      <c r="O43">
+        <v>85</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="12"/>
+        <v>32</v>
+      </c>
+      <c r="R43">
+        <f t="shared" si="13"/>
+        <v>19.5</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="14"/>
+        <v>13</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="15"/>
+        <v>21.5</v>
+      </c>
+      <c r="U43">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="V43">
+        <f t="shared" si="17"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B44">
+        <v>74</v>
+      </c>
+      <c r="C44">
+        <v>26</v>
+      </c>
+      <c r="D44">
+        <v>37</v>
+      </c>
+      <c r="E44">
+        <v>63</v>
+      </c>
+      <c r="G44">
+        <v>90</v>
+      </c>
+      <c r="H44">
+        <v>10</v>
+      </c>
+      <c r="I44">
+        <v>36</v>
+      </c>
+      <c r="J44">
+        <v>64</v>
+      </c>
+      <c r="L44">
+        <v>96</v>
+      </c>
+      <c r="M44">
+        <v>4</v>
+      </c>
+      <c r="N44">
+        <v>12</v>
+      </c>
+      <c r="O44">
+        <v>88</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="12"/>
+        <v>31.5</v>
+      </c>
+      <c r="R44">
+        <f t="shared" si="13"/>
+        <v>23</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="14"/>
+        <v>8</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="15"/>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="U44">
+        <f t="shared" si="16"/>
+        <v>8</v>
+      </c>
+      <c r="V44">
+        <f t="shared" si="17"/>
+        <v>12.833333333333332</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B45">
+        <v>72</v>
+      </c>
+      <c r="C45">
+        <v>28</v>
+      </c>
+      <c r="D45">
+        <v>39</v>
+      </c>
+      <c r="E45">
+        <v>61</v>
+      </c>
+      <c r="G45">
+        <v>81</v>
+      </c>
+      <c r="H45">
+        <v>19</v>
+      </c>
+      <c r="I45">
+        <v>44</v>
+      </c>
+      <c r="J45">
+        <v>56</v>
+      </c>
+      <c r="L45">
+        <v>95</v>
+      </c>
+      <c r="M45">
+        <v>5</v>
+      </c>
+      <c r="N45">
+        <v>15</v>
+      </c>
+      <c r="O45">
+        <v>85</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="12"/>
+        <v>33.5</v>
+      </c>
+      <c r="R45">
+        <f t="shared" si="13"/>
+        <v>31.5</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="T45">
+        <f t="shared" si="15"/>
+        <v>25</v>
+      </c>
+      <c r="U45">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="V45">
+        <f t="shared" si="17"/>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2761,7 +5649,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
-  <dimension ref="A2:AF4"/>
+  <dimension ref="A2:AF16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -2830,104 +5718,848 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D4">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="G4">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H4">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="J4">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="L4">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="M4">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="Q4">
         <f>AVERAGE(C4,D4)</f>
-        <v>28.5</v>
+        <v>25.5</v>
       </c>
       <c r="R4">
         <f>AVERAGE(H4,I4)</f>
-        <v>16</v>
+        <v>25.5</v>
       </c>
       <c r="S4">
         <f>AVERAGE(M4,N4)</f>
-        <v>39.5</v>
+        <v>9.5</v>
       </c>
       <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>28</v>
+        <v>20.166666666666668</v>
       </c>
       <c r="U4">
         <f>MIN(Q4:S4)</f>
-        <v>16</v>
+        <v>9.5</v>
       </c>
       <c r="V4">
         <f>T4-U4</f>
+        <v>10.666666666666668</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(Q4:Q19)</f>
+        <v>27.384615384615383</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(Q4:Q19)</f>
+        <v>3.1632910483245631</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(R4:R19)</f>
+        <v>28.076923076923077</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(R4:R19)</f>
+        <v>2.8346527847791889</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(S4:S19)</f>
+        <v>10.153846153846153</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(S4:S19)</f>
+        <v>2.8165035607455393</v>
+      </c>
+      <c r="AC4">
+        <f>AVERAGE(T4:T19)</f>
+        <v>21.871794871794869</v>
+      </c>
+      <c r="AD4">
+        <f>_xlfn.STDEV.S(T4:T19)</f>
+        <v>1.5872084832279494</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(V4:V19)</f>
+        <v>11.717948717948719</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(V4:V19)</f>
+        <v>1.9876757031403984</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>67</v>
+      </c>
+      <c r="C5">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>25</v>
+      </c>
+      <c r="E5">
+        <v>75</v>
+      </c>
+      <c r="G5">
+        <v>79</v>
+      </c>
+      <c r="H5">
+        <v>21</v>
+      </c>
+      <c r="I5">
+        <v>31</v>
+      </c>
+      <c r="J5">
+        <v>69</v>
+      </c>
+      <c r="L5">
+        <v>94</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+      <c r="N5">
+        <v>11</v>
+      </c>
+      <c r="O5">
+        <v>89</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q16" si="0">AVERAGE(C5,D5)</f>
+        <v>29</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R16" si="1">AVERAGE(H5,I5)</f>
+        <v>26</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S16" si="2">AVERAGE(M5,N5)</f>
+        <v>8.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T16" si="3">AVERAGE(Q5:S5)</f>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="U5">
+        <f t="shared" ref="U5:U16" si="4">MIN(Q5:S5)</f>
+        <v>8.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" ref="V5:V16" si="5">T5-U5</f>
+        <v>12.666666666666668</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>84</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>72</v>
+      </c>
+      <c r="G6">
+        <v>84</v>
+      </c>
+      <c r="H6">
+        <v>16</v>
+      </c>
+      <c r="I6">
+        <v>44</v>
+      </c>
+      <c r="J6">
+        <v>56</v>
+      </c>
+      <c r="L6">
+        <v>96</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+      <c r="N6">
+        <v>7</v>
+      </c>
+      <c r="O6">
+        <v>93</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>5.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>5.5</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>13.666666666666668</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>63</v>
+      </c>
+      <c r="C7">
+        <v>37</v>
+      </c>
+      <c r="D7">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>77</v>
+      </c>
+      <c r="G7">
+        <v>81</v>
+      </c>
+      <c r="H7">
+        <v>19</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>61</v>
+      </c>
+      <c r="L7">
+        <v>93</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+      <c r="N7">
+        <v>14</v>
+      </c>
+      <c r="O7">
+        <v>86</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>10.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>10.5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>12.666666666666668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>79</v>
+      </c>
+      <c r="G8">
+        <v>78</v>
+      </c>
+      <c r="H8">
+        <v>22</v>
+      </c>
+      <c r="I8">
+        <v>33</v>
+      </c>
+      <c r="J8">
+        <v>67</v>
+      </c>
+      <c r="L8">
+        <v>93</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
+      </c>
+      <c r="O8">
+        <v>90</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>8.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>19.666666666666668</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>8.5</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>11.166666666666668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>74</v>
+      </c>
+      <c r="C9">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>27</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="G9">
+        <v>85</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
+        <v>45</v>
+      </c>
+      <c r="J9">
+        <v>55</v>
+      </c>
+      <c r="L9">
+        <v>86</v>
+      </c>
+      <c r="M9">
+        <v>14</v>
+      </c>
+      <c r="N9">
+        <v>13</v>
+      </c>
+      <c r="O9">
+        <v>87</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>26.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>13.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>23.333333333333332</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>13.5</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>9.8333333333333321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>70</v>
+      </c>
+      <c r="C10">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <v>24</v>
+      </c>
+      <c r="E10">
+        <v>76</v>
+      </c>
+      <c r="G10">
+        <v>73</v>
+      </c>
+      <c r="H10">
+        <v>27</v>
+      </c>
+      <c r="I10">
+        <v>28</v>
+      </c>
+      <c r="J10">
+        <v>72</v>
+      </c>
+      <c r="L10">
+        <v>93</v>
+      </c>
+      <c r="M10">
+        <v>7</v>
+      </c>
+      <c r="N10">
         <v>12</v>
       </c>
-      <c r="W4">
-        <f>AVERAGE(Q4:Q12)</f>
-        <v>28.5</v>
-      </c>
-      <c r="X4" t="e">
-        <f>_xlfn.STDEV.S(Q4:Q12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(R4:R12)</f>
-        <v>16</v>
-      </c>
-      <c r="Z4" t="e">
-        <f>_xlfn.STDEV.S(R4:R12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(S4:S12)</f>
-        <v>39.5</v>
-      </c>
-      <c r="AB4" t="e">
-        <f>_xlfn.STDEV.S(S4:S12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC4">
-        <f>AVERAGE(T4:T12)</f>
+      <c r="O10">
+        <v>88</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>9.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>11.833333333333332</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>56</v>
+      </c>
+      <c r="C11">
+        <v>44</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>80</v>
+      </c>
+      <c r="G11">
+        <v>83</v>
+      </c>
+      <c r="H11">
+        <v>17</v>
+      </c>
+      <c r="I11">
+        <v>27</v>
+      </c>
+      <c r="J11">
+        <v>73</v>
+      </c>
+      <c r="L11">
+        <v>91</v>
+      </c>
+      <c r="M11">
+        <v>9</v>
+      </c>
+      <c r="N11">
+        <v>12</v>
+      </c>
+      <c r="O11">
+        <v>88</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>10.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>21.5</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>10.5</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>69</v>
+      </c>
+      <c r="C12">
+        <v>31</v>
+      </c>
+      <c r="D12">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>67</v>
+      </c>
+      <c r="G12">
+        <v>81</v>
+      </c>
+      <c r="H12">
+        <v>19</v>
+      </c>
+      <c r="I12">
+        <v>39</v>
+      </c>
+      <c r="J12">
+        <v>61</v>
+      </c>
+      <c r="L12">
+        <v>90</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <v>7</v>
+      </c>
+      <c r="O12">
+        <v>93</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="2"/>
+        <v>8.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="3"/>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="4"/>
+        <v>8.5</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="5"/>
+        <v>14.666666666666668</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>76</v>
+      </c>
+      <c r="C13">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>25</v>
+      </c>
+      <c r="E13">
+        <v>75</v>
+      </c>
+      <c r="G13">
+        <v>86</v>
+      </c>
+      <c r="H13">
+        <v>14</v>
+      </c>
+      <c r="I13">
+        <v>45</v>
+      </c>
+      <c r="J13">
+        <v>55</v>
+      </c>
+      <c r="L13">
+        <v>92</v>
+      </c>
+      <c r="M13">
+        <v>8</v>
+      </c>
+      <c r="N13">
+        <v>25</v>
+      </c>
+      <c r="O13">
+        <v>75</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>24.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>29.5</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="2"/>
+        <v>16.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="3"/>
+        <v>23.5</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="4"/>
+        <v>16.5</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>72</v>
+      </c>
+      <c r="C14">
         <v>28</v>
       </c>
-      <c r="AD4" t="e">
-        <f>_xlfn.STDEV.S(T4:T12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(V4:V12)</f>
-        <v>12</v>
-      </c>
-      <c r="AF4" t="e">
-        <f>_xlfn.STDEV.S(V4:V12)</f>
-        <v>#DIV/0!</v>
+      <c r="D14">
+        <v>26</v>
+      </c>
+      <c r="E14">
+        <v>74</v>
+      </c>
+      <c r="G14">
+        <v>83</v>
+      </c>
+      <c r="H14">
+        <v>17</v>
+      </c>
+      <c r="I14">
+        <v>49</v>
+      </c>
+      <c r="J14">
+        <v>51</v>
+      </c>
+      <c r="L14">
+        <v>92</v>
+      </c>
+      <c r="M14">
+        <v>8</v>
+      </c>
+      <c r="N14">
+        <v>18</v>
+      </c>
+      <c r="O14">
+        <v>82</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="3"/>
+        <v>24.333333333333332</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="5"/>
+        <v>11.333333333333332</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>78</v>
+      </c>
+      <c r="C15">
+        <v>22</v>
+      </c>
+      <c r="D15">
+        <v>33</v>
+      </c>
+      <c r="E15">
+        <v>67</v>
+      </c>
+      <c r="G15">
+        <v>83</v>
+      </c>
+      <c r="H15">
+        <v>17</v>
+      </c>
+      <c r="I15">
+        <v>44</v>
+      </c>
+      <c r="J15">
+        <v>56</v>
+      </c>
+      <c r="L15">
+        <v>93</v>
+      </c>
+      <c r="M15">
+        <v>7</v>
+      </c>
+      <c r="N15">
+        <v>9</v>
+      </c>
+      <c r="O15">
+        <v>91</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="0"/>
+        <v>27.5</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>30.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>76</v>
+      </c>
+      <c r="C16">
+        <v>24</v>
+      </c>
+      <c r="D16">
+        <v>36</v>
+      </c>
+      <c r="E16">
+        <v>64</v>
+      </c>
+      <c r="G16">
+        <v>89</v>
+      </c>
+      <c r="H16">
+        <v>11</v>
+      </c>
+      <c r="I16">
+        <v>40</v>
+      </c>
+      <c r="J16">
+        <v>60</v>
+      </c>
+      <c r="L16">
+        <v>89</v>
+      </c>
+      <c r="M16">
+        <v>11</v>
+      </c>
+      <c r="N16">
+        <v>9</v>
+      </c>
+      <c r="O16">
+        <v>91</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="1"/>
+        <v>25.5</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="3"/>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="5"/>
+        <v>11.833333333333332</v>
       </c>
     </row>
   </sheetData>
@@ -2937,7 +6569,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
-  <dimension ref="A2:AF4"/>
+  <dimension ref="A2:AF15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="21" max="21" width="10.44140625" customWidth="1"/>
@@ -3009,104 +6641,786 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C4">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G4">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="H4">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J4">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L4">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="M4">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="Q4">
         <f>AVERAGE(C4,D4)</f>
-        <v>25.5</v>
+        <v>38.5</v>
       </c>
       <c r="R4">
         <f>AVERAGE(H4,I4)</f>
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="S4">
         <f>AVERAGE(M4,N4)</f>
-        <v>39.5</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="U4">
         <f>MIN(Q4:S4)</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <f>T4-U4</f>
+        <v>18.5</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(Q4:Q19)</f>
+        <v>34.875</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(Q4:Q19)</f>
+        <v>3.9893323661074827</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(R4:R19)</f>
+        <v>32.625</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(R4:R19)</f>
+        <v>4.3123764804445024</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(S4:S19)</f>
+        <v>10.041666666666666</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(S4:S19)</f>
+        <v>1.8642367842843341</v>
+      </c>
+      <c r="AC4">
+        <f>AVERAGE(T4:T19)</f>
+        <v>25.847222222222225</v>
+      </c>
+      <c r="AD4">
+        <f>_xlfn.STDEV.S(T4:T19)</f>
+        <v>2.4827265206685523</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(V4:V19)</f>
+        <v>15.805555555555552</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(V4:V19)</f>
+        <v>2.6919570941293043</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>54</v>
+      </c>
+      <c r="C5">
+        <v>46</v>
+      </c>
+      <c r="D5">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <v>74</v>
+      </c>
+      <c r="G5">
+        <v>71</v>
+      </c>
+      <c r="H5">
+        <v>29</v>
+      </c>
+      <c r="I5">
+        <v>29</v>
+      </c>
+      <c r="J5">
+        <v>71</v>
+      </c>
+      <c r="L5">
+        <v>88</v>
+      </c>
+      <c r="M5">
+        <v>12</v>
+      </c>
+      <c r="N5">
         <v>13</v>
       </c>
-      <c r="W4">
-        <f>AVERAGE(Q4:Q12)</f>
+      <c r="O5">
+        <v>87</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q15" si="0">AVERAGE(C5,D5)</f>
+        <v>36</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R15" si="1">AVERAGE(H5,I5)</f>
+        <v>29</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S15" si="2">AVERAGE(M5,N5)</f>
+        <v>12.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T15" si="3">AVERAGE(Q5:S5)</f>
+        <v>25.833333333333332</v>
+      </c>
+      <c r="U5">
+        <f t="shared" ref="U5:U15" si="4">MIN(Q5:S5)</f>
+        <v>12.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" ref="V5:V15" si="5">T5-U5</f>
+        <v>13.333333333333332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>43</v>
+      </c>
+      <c r="C6">
+        <v>57</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>48</v>
+      </c>
+      <c r="H6">
+        <v>52</v>
+      </c>
+      <c r="I6">
+        <v>24</v>
+      </c>
+      <c r="J6">
+        <v>76</v>
+      </c>
+      <c r="L6">
+        <v>90</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>16</v>
+      </c>
+      <c r="O6">
+        <v>84</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>38.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>29.833333333333332</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>16.833333333333332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>45</v>
+      </c>
+      <c r="C7">
+        <v>55</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>73</v>
+      </c>
+      <c r="G7">
+        <v>57</v>
+      </c>
+      <c r="H7">
+        <v>43</v>
+      </c>
+      <c r="I7">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>71</v>
+      </c>
+      <c r="L7">
+        <v>89</v>
+      </c>
+      <c r="M7">
+        <v>11</v>
+      </c>
+      <c r="N7">
+        <v>8</v>
+      </c>
+      <c r="O7">
+        <v>92</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>9.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>28.833333333333332</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>19.333333333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>73</v>
+      </c>
+      <c r="C8">
+        <v>27</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>73</v>
+      </c>
+      <c r="G8">
+        <v>73</v>
+      </c>
+      <c r="H8">
+        <v>27</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>66</v>
+      </c>
+      <c r="L8">
+        <v>86</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+      <c r="N8">
+        <v>6</v>
+      </c>
+      <c r="O8">
+        <v>94</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>30.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>22.5</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>50</v>
+      </c>
+      <c r="C9">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>28</v>
+      </c>
+      <c r="E9">
+        <v>72</v>
+      </c>
+      <c r="G9">
+        <v>49</v>
+      </c>
+      <c r="H9">
+        <v>51</v>
+      </c>
+      <c r="I9">
+        <v>31</v>
+      </c>
+      <c r="J9">
+        <v>69</v>
+      </c>
+      <c r="L9">
+        <v>85</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
+      <c r="O9">
+        <v>96</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>9.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>29.833333333333332</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>20.333333333333332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>74</v>
+      </c>
+      <c r="C10">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>36</v>
+      </c>
+      <c r="E10">
+        <v>64</v>
+      </c>
+      <c r="G10">
+        <v>76</v>
+      </c>
+      <c r="H10">
+        <v>24</v>
+      </c>
+      <c r="I10">
+        <v>44</v>
+      </c>
+      <c r="J10">
+        <v>56</v>
+      </c>
+      <c r="L10">
+        <v>90</v>
+      </c>
+      <c r="M10">
+        <v>10</v>
+      </c>
+      <c r="N10">
+        <v>7</v>
+      </c>
+      <c r="O10">
+        <v>93</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>8.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>24.5</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>8.5</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>68</v>
+      </c>
+      <c r="C11">
+        <v>32</v>
+      </c>
+      <c r="D11">
+        <v>32</v>
+      </c>
+      <c r="E11">
+        <v>68</v>
+      </c>
+      <c r="G11">
+        <v>77</v>
+      </c>
+      <c r="H11">
+        <v>23</v>
+      </c>
+      <c r="I11">
+        <v>42</v>
+      </c>
+      <c r="J11">
+        <v>58</v>
+      </c>
+      <c r="L11">
+        <v>93</v>
+      </c>
+      <c r="M11">
+        <v>7</v>
+      </c>
+      <c r="N11">
+        <v>11</v>
+      </c>
+      <c r="O11">
+        <v>89</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>32.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>24.5</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="5"/>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>59</v>
+      </c>
+      <c r="C12">
+        <v>41</v>
+      </c>
+      <c r="D12">
+        <v>24</v>
+      </c>
+      <c r="E12">
+        <v>76</v>
+      </c>
+      <c r="G12">
+        <v>64</v>
+      </c>
+      <c r="H12">
+        <v>36</v>
+      </c>
+      <c r="I12">
+        <v>23</v>
+      </c>
+      <c r="J12">
+        <v>77</v>
+      </c>
+      <c r="L12">
+        <v>90</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <v>13</v>
+      </c>
+      <c r="O12">
+        <v>87</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>32.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>29.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="2"/>
+        <v>11.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="3"/>
+        <v>24.5</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="4"/>
+        <v>11.5</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>53</v>
+      </c>
+      <c r="C13">
+        <v>47</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>80</v>
+      </c>
+      <c r="G13">
+        <v>70</v>
+      </c>
+      <c r="H13">
+        <v>30</v>
+      </c>
+      <c r="I13">
+        <v>28</v>
+      </c>
+      <c r="J13">
+        <v>72</v>
+      </c>
+      <c r="L13">
+        <v>92</v>
+      </c>
+      <c r="M13">
+        <v>8</v>
+      </c>
+      <c r="N13">
+        <v>6</v>
+      </c>
+      <c r="O13">
+        <v>94</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>33.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="3"/>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="5"/>
+        <v>16.166666666666668</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>66</v>
+      </c>
+      <c r="C14">
+        <v>34</v>
+      </c>
+      <c r="D14">
+        <v>36</v>
+      </c>
+      <c r="E14">
+        <v>64</v>
+      </c>
+      <c r="G14">
+        <v>77</v>
+      </c>
+      <c r="H14">
+        <v>23</v>
+      </c>
+      <c r="I14">
+        <v>28</v>
+      </c>
+      <c r="J14">
+        <v>72</v>
+      </c>
+      <c r="L14">
+        <v>83</v>
+      </c>
+      <c r="M14">
+        <v>17</v>
+      </c>
+      <c r="N14">
+        <v>7</v>
+      </c>
+      <c r="O14">
+        <v>93</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="1"/>
         <v>25.5</v>
       </c>
-      <c r="X4" t="e">
-        <f>_xlfn.STDEV.S(Q4:Q12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(R4:R12)</f>
-        <v>13</v>
-      </c>
-      <c r="Z4" t="e">
-        <f>_xlfn.STDEV.S(R4:R12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(S4:S12)</f>
-        <v>39.5</v>
-      </c>
-      <c r="AB4" t="e">
-        <f>_xlfn.STDEV.S(S4:S12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC4">
-        <f>AVERAGE(T4:T12)</f>
+      <c r="S14">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="3"/>
+        <v>24.166666666666668</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="5"/>
+        <v>12.166666666666668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>57</v>
+      </c>
+      <c r="C15">
+        <v>43</v>
+      </c>
+      <c r="D15">
         <v>26</v>
       </c>
-      <c r="AD4" t="e">
-        <f>_xlfn.STDEV.S(T4:T12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(V4:V12)</f>
-        <v>13</v>
-      </c>
-      <c r="AF4" t="e">
-        <f>_xlfn.STDEV.S(V4:V12)</f>
-        <v>#DIV/0!</v>
+      <c r="E15">
+        <v>74</v>
+      </c>
+      <c r="G15">
+        <v>56</v>
+      </c>
+      <c r="H15">
+        <v>44</v>
+      </c>
+      <c r="I15">
+        <v>23</v>
+      </c>
+      <c r="J15">
+        <v>77</v>
+      </c>
+      <c r="L15">
+        <v>85</v>
+      </c>
+      <c r="M15">
+        <v>15</v>
+      </c>
+      <c r="N15">
+        <v>5</v>
+      </c>
+      <c r="O15">
+        <v>95</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="0"/>
+        <v>34.5</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>33.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="5"/>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
